--- a/output/pdf_financials_xlsx/TRBC.xlsx
+++ b/output/pdf_financials_xlsx/TRBC.xlsx
@@ -6113,46 +6113,46 @@
         <v>1.188441</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.188441</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.279441</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.399441</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.399441</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.399441</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.399441</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.399441</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.559441</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.559441</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.559441</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.069059</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.201844</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.554307</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.986537</v>
       </c>
     </row>
     <row r="93">
@@ -9594,7 +9594,11 @@
           <t>Share-based payments reserve 5</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -14728,7 +14732,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16320,7 +16328,11 @@
           <t>Share-based payments reserve 8</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16789,7 +16801,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -19074,7 +19090,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRBC.xlsx
+++ b/output/pdf_financials_xlsx/TRBC.xlsx
@@ -1083,40 +1083,40 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.024046</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005626</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010604</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.008659</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.005733</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005619</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.012359</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.016011</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.008144999999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003352</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.015737</v>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
@@ -2163,40 +2163,40 @@
         <v>-0.01682</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.160958</v>
+        <v>0.160402</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.846492</v>
+        <v>-0.870538</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.966253</v>
+        <v>-1.971879</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.658787</v>
+        <v>-1.669391</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.12755</v>
+        <v>-0.136209</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.424108</v>
+        <v>-0.429841</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.283278</v>
+        <v>0.277659</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.505982</v>
+        <v>-0.5183410000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.29796</v>
+        <v>-0.313971</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.133261</v>
+        <v>-0.141406</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.15249</v>
+        <v>-0.155842</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.142606</v>
+        <v>-3.158343</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2291,40 +2291,40 @@
         <v>-0.01682</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.160958</v>
+        <v>0.160402</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.846492</v>
+        <v>-0.870538</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.966253</v>
+        <v>-1.971879</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.658787</v>
+        <v>-1.669391</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.12755</v>
+        <v>-0.136209</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.424108</v>
+        <v>-0.429841</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.283278</v>
+        <v>0.277659</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.505982</v>
+        <v>-0.5183410000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.29796</v>
+        <v>-0.313971</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.133261</v>
+        <v>-0.141406</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.15249</v>
+        <v>-0.155842</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.142606</v>
+        <v>-3.158343</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2604,40 +2604,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.428264</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.368278</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.212575</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.319487</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.716102</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.464928</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.364444</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.019572</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.377315</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.832767</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.642209</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.487641</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.04478</v>
@@ -2720,40 +2720,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.428264</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.368278</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.212575</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.319487</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.716102</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.464928</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.364444</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.019572</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.377315</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.832767</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.642209</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.487641</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.04478</v>
@@ -3416,40 +3416,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.430764</v>
+        <v>0.0025</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.58453</v>
+        <v>0.216252</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.215757</v>
+        <v>0.003182</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.56899</v>
+        <v>0.249503</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.718702</v>
+        <v>0.0026</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.467528</v>
+        <v>0.0026</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.022172</v>
+        <v>0.0026</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.379915</v>
+        <v>0.0026</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.84829</v>
+        <v>0.015523</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.644809</v>
+        <v>0.0026</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.490241</v>
+        <v>0.0026</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1.1e-05</v>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -35017,7 +35017,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -36297,7 +36297,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">

--- a/output/pdf_financials_xlsx/TRBC.xlsx
+++ b/output/pdf_financials_xlsx/TRBC.xlsx
@@ -760,7 +760,7 @@
         <v>0.170583</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.153196</v>
+        <v>0.178725</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.116164</v>
@@ -1342,10 +1342,10 @@
         <v>0.160958</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.846492</v>
+        <v>-1.196492</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.966253</v>
+        <v>-1.774253</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-1.658787</v>
@@ -1403,13 +1403,13 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.158</v>
+        <v>-0.158</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.35</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.192</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -2166,10 +2166,10 @@
         <v>0.160402</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.870538</v>
+        <v>-1.220538</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.971879</v>
+        <v>-1.779879</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.669391</v>
@@ -2294,10 +2294,10 @@
         <v>0.160402</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.870538</v>
+        <v>-1.220538</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.971879</v>
+        <v>-1.779879</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.669391</v>
@@ -2450,10 +2450,10 @@
         <v>98.16225350712608</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-29.25218054111519</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-10.8214555646799</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -6593,43 +6593,43 @@
         <v>0.05165</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.022366</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004483</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.016148</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.006789</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.0006890000000000001</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003042</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.005928</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.00227</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000119</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011957</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012018</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001443</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-5.5e-05</v>
       </c>
     </row>
     <row r="102">
@@ -6889,37 +6889,37 @@
         <v>-0.005467</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.010918</v>
+        <v>0.027066</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.007512</v>
+        <v>0.014301</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.209846</v>
+        <v>0.210535</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.041824</v>
+        <v>-0.044866</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.190206</v>
+        <v>-0.184278</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.023577</v>
+        <v>-0.021307</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.040771</v>
+        <v>0.040652</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.191986</v>
+        <v>0.180029</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.172499</v>
+        <v>-0.184517</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.135846</v>
+        <v>-0.137289</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.056001</v>
+        <v>0.055946</v>
       </c>
     </row>
     <row r="107">
@@ -22429,7 +22429,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -25304,7 +25308,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -28064,7 +28072,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -28561,7 +28573,11 @@
           <t>Increase in GST/HST receivable</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -29367,7 +29383,11 @@
           <t>Decrease (increase) in GST/HST receivable</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -32001,7 +32021,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -44292,7 +44316,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -46706,7 +46734,11 @@
           <t>Professional and director fees</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -48508,7 +48540,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 9)</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
